--- a/examples/basic/流域蒸散发量及产流量计算/result.xlsx
+++ b/examples/basic/流域蒸散发量及产流量计算/result.xlsx
@@ -872,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>154.2</v>
+        <v>156</v>
       </c>
       <c r="O7">
         <v>1</v>
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>151.6</v>
+        <v>145</v>
       </c>
       <c r="O8">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1002,10 +1002,10 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>149</v>
+        <v>137.1</v>
       </c>
       <c r="O9">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>148.9</v>
+        <v>131.2</v>
       </c>
       <c r="O10">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -1132,10 +1132,10 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>144.8</v>
+        <v>130.8</v>
       </c>
       <c r="O11">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -1197,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>139.7</v>
+        <v>123.2</v>
       </c>
       <c r="O12">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1262,10 +1262,10 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>134.8</v>
+        <v>115</v>
       </c>
       <c r="O13">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1327,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>129.3</v>
+        <v>108.2</v>
       </c>
       <c r="O14">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1392,10 +1392,10 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>124.1</v>
+        <v>101.1</v>
       </c>
       <c r="O15">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -1454,31 +1454,31 @@
         <v>84.59999999999999</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="N16">
-        <v>129.6</v>
+        <v>95</v>
       </c>
       <c r="O16">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>0.2545454545454545</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -1492,22 +1492,22 @@
         <v>4.6</v>
       </c>
       <c r="D17">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H17">
-        <v>-4.6</v>
+        <v>-4.5</v>
       </c>
       <c r="I17">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="J17">
         <v>44.6</v>
@@ -1516,16 +1516,16 @@
         <v>40</v>
       </c>
       <c r="L17">
-        <v>90.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="M17">
         <v>0</v>
       </c>
       <c r="N17">
-        <v>125.2</v>
+        <v>100.5</v>
       </c>
       <c r="O17">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -1557,40 +1557,40 @@
         <v>6.5</v>
       </c>
       <c r="D18">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="H18">
-        <v>-5.1</v>
+        <v>-4.8</v>
       </c>
       <c r="I18">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>44.6</v>
+        <v>44.2</v>
       </c>
       <c r="K18">
         <v>40</v>
       </c>
       <c r="L18">
-        <v>85.5</v>
+        <v>84.2</v>
       </c>
       <c r="M18">
         <v>0</v>
       </c>
       <c r="N18">
-        <v>119.2</v>
+        <v>94.5</v>
       </c>
       <c r="O18">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -1625,37 +1625,37 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H19">
-        <v>-4.2</v>
+        <v>-4.1</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>40.5</v>
+        <v>39.5</v>
       </c>
       <c r="K19">
         <v>40</v>
       </c>
       <c r="L19">
-        <v>80.5</v>
+        <v>79.5</v>
       </c>
       <c r="M19">
         <v>0</v>
       </c>
       <c r="N19">
-        <v>113.9</v>
+        <v>88.3</v>
       </c>
       <c r="O19">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -1705,40 +1705,40 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>36.2</v>
+        <v>35.3</v>
       </c>
       <c r="K20">
         <v>40</v>
       </c>
       <c r="L20">
-        <v>76.2</v>
+        <v>75.3</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="N20">
-        <v>122.5</v>
+        <v>83</v>
       </c>
       <c r="O20">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>0.2209302325581395</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -1767,25 +1767,25 @@
         <v>-2.5</v>
       </c>
       <c r="I21">
-        <v>8.6</v>
+        <v>6.7</v>
       </c>
       <c r="J21">
-        <v>36.2</v>
+        <v>35.3</v>
       </c>
       <c r="K21">
         <v>40</v>
       </c>
       <c r="L21">
-        <v>84.8</v>
+        <v>82</v>
       </c>
       <c r="M21">
         <v>0</v>
       </c>
       <c r="N21">
-        <v>121.4</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O21">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -1832,43 +1832,43 @@
         <v>2.2</v>
       </c>
       <c r="I22">
-        <v>6.1</v>
+        <v>4.2</v>
       </c>
       <c r="J22">
-        <v>36.2</v>
+        <v>35.3</v>
       </c>
       <c r="K22">
         <v>40</v>
       </c>
       <c r="L22">
-        <v>82.3</v>
+        <v>79.5</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N22">
-        <v>123.6</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="O22">
+        <v>0.2</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
         <v>0.4</v>
       </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
       <c r="R22">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>0.2272727272727273</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -1897,43 +1897,43 @@
         <v>49.8</v>
       </c>
       <c r="I23">
-        <v>8.300000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="J23">
-        <v>36.2</v>
+        <v>35.3</v>
       </c>
       <c r="K23">
         <v>40</v>
       </c>
       <c r="L23">
-        <v>84.5</v>
+        <v>81.2</v>
       </c>
       <c r="M23">
-        <v>14.3</v>
+        <v>17.1</v>
       </c>
       <c r="N23">
-        <v>123.6</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O23">
+        <v>0.2</v>
+      </c>
+      <c r="P23">
+        <v>16.2</v>
+      </c>
+      <c r="Q23">
+        <v>0.9</v>
+      </c>
+      <c r="R23">
+        <v>2.7</v>
+      </c>
+      <c r="S23">
         <v>0.4</v>
       </c>
-      <c r="P23">
-        <v>13.6</v>
-      </c>
-      <c r="Q23">
-        <v>0.7</v>
-      </c>
-      <c r="R23">
-        <v>6.9</v>
-      </c>
-      <c r="S23">
-        <v>0.9</v>
-      </c>
       <c r="T23">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="U23">
-        <v>0.2871485943775101</v>
+        <v>0.3433734939759037</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -1965,22 +1965,22 @@
         <v>20</v>
       </c>
       <c r="J24">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K24">
         <v>40</v>
       </c>
       <c r="L24">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
       <c r="N24">
-        <v>155.8</v>
+        <v>140.4</v>
       </c>
       <c r="O24">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -2030,22 +2030,22 @@
         <v>19.2</v>
       </c>
       <c r="J25">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K25">
         <v>40</v>
       </c>
       <c r="L25">
-        <v>119.2</v>
+        <v>113.2</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>153.7</v>
+        <v>138.8</v>
       </c>
       <c r="O25">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -2095,22 +2095,22 @@
         <v>15.3</v>
       </c>
       <c r="J26">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K26">
         <v>40</v>
       </c>
       <c r="L26">
-        <v>115.3</v>
+        <v>109.3</v>
       </c>
       <c r="M26">
         <v>0</v>
       </c>
       <c r="N26">
-        <v>152</v>
+        <v>131.7</v>
       </c>
       <c r="O26">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -2160,22 +2160,22 @@
         <v>12.9</v>
       </c>
       <c r="J27">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K27">
         <v>40</v>
       </c>
       <c r="L27">
-        <v>112.9</v>
+        <v>106.9</v>
       </c>
       <c r="M27">
         <v>0</v>
       </c>
       <c r="N27">
-        <v>148.8</v>
+        <v>127.6</v>
       </c>
       <c r="O27">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -2225,22 +2225,22 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J28">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K28">
         <v>40</v>
       </c>
       <c r="L28">
-        <v>108.7</v>
+        <v>102.7</v>
       </c>
       <c r="M28">
         <v>0</v>
       </c>
       <c r="N28">
-        <v>147.4</v>
+        <v>120.8</v>
       </c>
       <c r="O28">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -2290,22 +2290,22 @@
         <v>7.1</v>
       </c>
       <c r="J29">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K29">
         <v>40</v>
       </c>
       <c r="L29">
-        <v>107.1</v>
+        <v>101.1</v>
       </c>
       <c r="M29">
         <v>0</v>
       </c>
       <c r="N29">
-        <v>142</v>
+        <v>118.3</v>
       </c>
       <c r="O29">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -2340,37 +2340,37 @@
         <v>1.2</v>
       </c>
       <c r="E30">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="H30">
-        <v>-6</v>
+        <v>-5.5</v>
       </c>
       <c r="I30">
         <v>1.2</v>
       </c>
       <c r="J30">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K30">
         <v>40</v>
       </c>
       <c r="L30">
-        <v>101.2</v>
+        <v>95.2</v>
       </c>
       <c r="M30">
         <v>0</v>
       </c>
       <c r="N30">
-        <v>135.9</v>
+        <v>109.6</v>
       </c>
       <c r="O30">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -2405,37 +2405,37 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="H31">
-        <v>-5.6</v>
+        <v>-5</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>55.2</v>
+        <v>49.7</v>
       </c>
       <c r="K31">
         <v>40</v>
       </c>
       <c r="L31">
-        <v>95.2</v>
+        <v>89.7</v>
       </c>
       <c r="M31">
         <v>0</v>
       </c>
       <c r="N31">
-        <v>129.8</v>
+        <v>101.8</v>
       </c>
       <c r="O31">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -2470,37 +2470,37 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="H32">
-        <v>-6.4</v>
+        <v>-5.8</v>
       </c>
       <c r="I32">
         <v>0</v>
       </c>
       <c r="J32">
-        <v>49.6</v>
+        <v>44.6</v>
       </c>
       <c r="K32">
         <v>40</v>
       </c>
       <c r="L32">
-        <v>89.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="M32">
         <v>0</v>
       </c>
       <c r="N32">
-        <v>122.4</v>
+        <v>95</v>
       </c>
       <c r="O32">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -2535,37 +2535,37 @@
         <v>3.9</v>
       </c>
       <c r="E33">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H33">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>43.1</v>
+        <v>38.8</v>
       </c>
       <c r="K33">
         <v>40</v>
       </c>
       <c r="L33">
-        <v>83.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="M33">
         <v>0</v>
       </c>
       <c r="N33">
-        <v>120.6</v>
+        <v>87.5</v>
       </c>
       <c r="O33">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -2600,37 +2600,37 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H34">
-        <v>-4</v>
+        <v>-3.6</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>41.6</v>
+        <v>37.5</v>
       </c>
       <c r="K34">
         <v>40</v>
       </c>
       <c r="L34">
-        <v>81.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="M34">
         <v>0</v>
       </c>
       <c r="N34">
-        <v>115.8</v>
+        <v>85.7</v>
       </c>
       <c r="O34">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -2680,40 +2680,40 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>37.7</v>
+        <v>33.9</v>
       </c>
       <c r="K35">
         <v>40</v>
       </c>
       <c r="L35">
-        <v>77.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N35">
-        <v>134.5</v>
+        <v>81.3</v>
       </c>
       <c r="O35">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>0.2299465240641711</v>
       </c>
     </row>
     <row r="36" spans="1:21">
@@ -2742,25 +2742,25 @@
         <v>-5.2</v>
       </c>
       <c r="I36">
-        <v>18.7</v>
+        <v>14.4</v>
       </c>
       <c r="J36">
-        <v>37.7</v>
+        <v>33.9</v>
       </c>
       <c r="K36">
         <v>40</v>
       </c>
       <c r="L36">
-        <v>96.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="M36">
         <v>0</v>
       </c>
       <c r="N36">
-        <v>131.6</v>
+        <v>100</v>
       </c>
       <c r="O36">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -2807,25 +2807,25 @@
         <v>-5</v>
       </c>
       <c r="I37">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J37">
-        <v>37.7</v>
+        <v>33.9</v>
       </c>
       <c r="K37">
         <v>40</v>
       </c>
       <c r="L37">
-        <v>91.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="M37">
         <v>0</v>
       </c>
       <c r="N37">
-        <v>125.9</v>
+        <v>93</v>
       </c>
       <c r="O37">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -2857,40 +2857,40 @@
         <v>6.9</v>
       </c>
       <c r="D38">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="F38">
         <v>0</v>
       </c>
       <c r="G38">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="H38">
-        <v>-6.3</v>
+        <v>-5.4</v>
       </c>
       <c r="I38">
-        <v>8.5</v>
+        <v>4.2</v>
       </c>
       <c r="J38">
-        <v>37.7</v>
+        <v>33.9</v>
       </c>
       <c r="K38">
         <v>40</v>
       </c>
       <c r="L38">
-        <v>86.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="M38">
         <v>0</v>
       </c>
       <c r="N38">
-        <v>118.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="O38">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -2922,40 +2922,40 @@
         <v>2.7</v>
       </c>
       <c r="D39">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="E39">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="F39">
         <v>0</v>
       </c>
       <c r="G39">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="H39">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="I39">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>37.7</v>
+        <v>32.7</v>
       </c>
       <c r="K39">
         <v>40</v>
       </c>
       <c r="L39">
-        <v>79.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="M39">
         <v>0</v>
       </c>
       <c r="N39">
-        <v>115.5</v>
+        <v>79.8</v>
       </c>
       <c r="O39">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -3005,40 +3005,40 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <v>37.5</v>
+        <v>31.3</v>
       </c>
       <c r="K40">
         <v>40</v>
       </c>
       <c r="L40">
-        <v>77.5</v>
+        <v>71.3</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="N40">
-        <v>121.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="O40">
+        <v>0.2</v>
+      </c>
+      <c r="P40">
+        <v>0.7</v>
+      </c>
+      <c r="Q40">
+        <v>0.5</v>
+      </c>
+      <c r="R40">
         <v>0.3</v>
       </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="Q40">
-        <v>0</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
       <c r="S40">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="41" spans="1:21">
@@ -3067,25 +3067,25 @@
         <v>-4.1</v>
       </c>
       <c r="I41">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="J41">
-        <v>37.5</v>
+        <v>31.3</v>
       </c>
       <c r="K41">
         <v>40</v>
       </c>
       <c r="L41">
-        <v>83.5</v>
+        <v>76.2</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
       <c r="N41">
-        <v>117.9</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="O41">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -3132,43 +3132,43 @@
         <v>1.5</v>
       </c>
       <c r="I42">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J42">
-        <v>37.5</v>
+        <v>31.3</v>
       </c>
       <c r="K42">
         <v>40</v>
       </c>
       <c r="L42">
-        <v>79.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N42">
-        <v>119.4</v>
+        <v>79</v>
       </c>
       <c r="O42">
+        <v>0.2</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
         <v>0.3</v>
       </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42">
-        <v>0</v>
-      </c>
       <c r="R42">
         <v>0</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="43" spans="1:21">
@@ -3182,40 +3182,40 @@
         <v>6.7</v>
       </c>
       <c r="D43">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="E43">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="H43">
-        <v>-5.5</v>
+        <v>-4.4</v>
       </c>
       <c r="I43">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J43">
-        <v>37.5</v>
+        <v>31.3</v>
       </c>
       <c r="K43">
         <v>40</v>
       </c>
       <c r="L43">
-        <v>80.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="M43">
         <v>0</v>
       </c>
       <c r="N43">
-        <v>112.9</v>
+        <v>80.5</v>
       </c>
       <c r="O43">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P43">
         <v>0</v>
@@ -3250,37 +3250,37 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
       <c r="G44">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="H44">
-        <v>-4</v>
+        <v>-3.3</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>35.4</v>
+        <v>28.9</v>
       </c>
       <c r="K44">
         <v>40</v>
       </c>
       <c r="L44">
-        <v>75.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="M44">
         <v>0</v>
       </c>
       <c r="N44">
-        <v>107.8</v>
+        <v>75</v>
       </c>
       <c r="O44">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P44">
         <v>0</v>
@@ -3315,37 +3315,37 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
       <c r="G45">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="H45">
-        <v>-3.6</v>
+        <v>-2.9</v>
       </c>
       <c r="I45">
         <v>0</v>
       </c>
       <c r="J45">
-        <v>31.4</v>
+        <v>25.6</v>
       </c>
       <c r="K45">
         <v>40</v>
       </c>
       <c r="L45">
-        <v>71.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="M45">
         <v>0</v>
       </c>
       <c r="N45">
-        <v>103.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="O45">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P45">
         <v>0</v>
@@ -3380,37 +3380,37 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="F46">
         <v>0</v>
       </c>
       <c r="G46">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="H46">
-        <v>-3.9</v>
+        <v>-3.1</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>27.9</v>
+        <v>22.7</v>
       </c>
       <c r="K46">
         <v>40</v>
       </c>
       <c r="L46">
-        <v>67.90000000000001</v>
+        <v>62.7</v>
       </c>
       <c r="M46">
         <v>0</v>
       </c>
       <c r="N46">
-        <v>98.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O46">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P46">
         <v>0</v>
@@ -3445,37 +3445,37 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="F47">
         <v>0</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="H47">
-        <v>-3</v>
+        <v>-2.4</v>
       </c>
       <c r="I47">
         <v>0</v>
       </c>
       <c r="J47">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="K47">
         <v>40</v>
       </c>
       <c r="L47">
-        <v>64</v>
+        <v>59.5</v>
       </c>
       <c r="M47">
         <v>0</v>
       </c>
       <c r="N47">
-        <v>94.09999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="O47">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P47">
         <v>0</v>
@@ -3525,40 +3525,40 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <v>21</v>
+        <v>17.1</v>
       </c>
       <c r="K48">
         <v>40</v>
       </c>
       <c r="L48">
-        <v>61</v>
+        <v>57.1</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N48">
-        <v>121.3</v>
+        <v>61.1</v>
       </c>
       <c r="O48">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>0.1801470588235294</v>
       </c>
     </row>
     <row r="49" spans="1:21">
@@ -3590,22 +3590,22 @@
         <v>20</v>
       </c>
       <c r="J49">
-        <v>28.2</v>
+        <v>19.5</v>
       </c>
       <c r="K49">
         <v>40</v>
       </c>
       <c r="L49">
-        <v>88.2</v>
+        <v>79.5</v>
       </c>
       <c r="M49">
         <v>0</v>
       </c>
       <c r="N49">
-        <v>124.4</v>
+        <v>88.3</v>
       </c>
       <c r="O49">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="P49">
         <v>0</v>
@@ -3655,22 +3655,22 @@
         <v>16.6</v>
       </c>
       <c r="J50">
-        <v>28.2</v>
+        <v>19.5</v>
       </c>
       <c r="K50">
         <v>40</v>
       </c>
       <c r="L50">
-        <v>84.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M50">
         <v>0</v>
       </c>
       <c r="N50">
-        <v>117.1</v>
+        <v>84</v>
       </c>
       <c r="O50">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P50">
         <v>0</v>
@@ -3720,22 +3720,22 @@
         <v>10.5</v>
       </c>
       <c r="J51">
-        <v>28.2</v>
+        <v>19.5</v>
       </c>
       <c r="K51">
         <v>40</v>
       </c>
       <c r="L51">
-        <v>78.7</v>
+        <v>70</v>
       </c>
       <c r="M51">
         <v>0</v>
       </c>
       <c r="N51">
-        <v>112</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="O51">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P51">
         <v>0</v>
@@ -3770,37 +3770,37 @@
         <v>6.4</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F52">
         <v>0</v>
       </c>
       <c r="G52">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="H52">
-        <v>-7.4</v>
+        <v>-7.1</v>
       </c>
       <c r="I52">
         <v>6.4</v>
       </c>
       <c r="J52">
-        <v>28.2</v>
+        <v>19.5</v>
       </c>
       <c r="K52">
         <v>40</v>
       </c>
       <c r="L52">
-        <v>74.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M52">
         <v>0</v>
       </c>
       <c r="N52">
-        <v>102.3</v>
+        <v>71.5</v>
       </c>
       <c r="O52">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P52">
         <v>0</v>
@@ -3835,37 +3835,37 @@
         <v>0.3</v>
       </c>
       <c r="E53">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="F53">
         <v>0</v>
       </c>
       <c r="G53">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="H53">
-        <v>-2.6</v>
+        <v>-1.8</v>
       </c>
       <c r="I53">
         <v>0</v>
       </c>
       <c r="J53">
-        <v>27.2</v>
+        <v>18.8</v>
       </c>
       <c r="K53">
         <v>40</v>
       </c>
       <c r="L53">
-        <v>67.2</v>
+        <v>58.8</v>
       </c>
       <c r="M53">
         <v>0</v>
       </c>
       <c r="N53">
-        <v>98.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="O53">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P53">
         <v>0</v>
@@ -3900,37 +3900,37 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="F54">
         <v>0</v>
       </c>
       <c r="G54">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="H54">
-        <v>-2.7</v>
+        <v>-1.9</v>
       </c>
       <c r="I54">
         <v>0</v>
       </c>
       <c r="J54">
-        <v>24.6</v>
+        <v>17</v>
       </c>
       <c r="K54">
         <v>40</v>
       </c>
       <c r="L54">
-        <v>64.59999999999999</v>
+        <v>57</v>
       </c>
       <c r="M54">
         <v>0</v>
       </c>
       <c r="N54">
-        <v>95.3</v>
+        <v>60.9</v>
       </c>
       <c r="O54">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -3965,37 +3965,37 @@
         <v>0.7</v>
       </c>
       <c r="E55">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="F55">
         <v>0</v>
       </c>
       <c r="G55">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="H55">
-        <v>-2.1</v>
+        <v>-1.5</v>
       </c>
       <c r="I55">
         <v>0</v>
       </c>
       <c r="J55">
-        <v>21.9</v>
+        <v>15.1</v>
       </c>
       <c r="K55">
         <v>40</v>
       </c>
       <c r="L55">
-        <v>61.9</v>
+        <v>55.1</v>
       </c>
       <c r="M55">
         <v>0</v>
       </c>
       <c r="N55">
-        <v>92.40000000000001</v>
+        <v>58.8</v>
       </c>
       <c r="O55">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -4030,37 +4030,37 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="F56">
         <v>0</v>
       </c>
       <c r="G56">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="H56">
-        <v>-2.7</v>
+        <v>-1.8</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>19.8</v>
+        <v>13.7</v>
       </c>
       <c r="K56">
         <v>40</v>
       </c>
       <c r="L56">
-        <v>59.8</v>
+        <v>53.7</v>
       </c>
       <c r="M56">
         <v>0</v>
       </c>
       <c r="N56">
-        <v>88.7</v>
+        <v>57.1</v>
       </c>
       <c r="O56">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P56">
         <v>0</v>
@@ -4095,37 +4095,37 @@
         <v>0.5</v>
       </c>
       <c r="E57">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="F57">
         <v>0</v>
       </c>
       <c r="G57">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="H57">
-        <v>-2</v>
+        <v>-1.4</v>
       </c>
       <c r="I57">
         <v>0</v>
       </c>
       <c r="J57">
-        <v>17.1</v>
+        <v>11.8</v>
       </c>
       <c r="K57">
         <v>40</v>
       </c>
       <c r="L57">
-        <v>57.1</v>
+        <v>51.8</v>
       </c>
       <c r="M57">
         <v>0</v>
       </c>
       <c r="N57">
-        <v>85.90000000000001</v>
+        <v>55</v>
       </c>
       <c r="O57">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P57">
         <v>0</v>
@@ -4160,37 +4160,37 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="F58">
         <v>0</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="H58">
-        <v>-2</v>
+        <v>-1.4</v>
       </c>
       <c r="I58">
         <v>0</v>
       </c>
       <c r="J58">
-        <v>15.2</v>
+        <v>10.5</v>
       </c>
       <c r="K58">
         <v>40</v>
       </c>
       <c r="L58">
-        <v>55.2</v>
+        <v>50.5</v>
       </c>
       <c r="M58">
         <v>0</v>
       </c>
       <c r="N58">
-        <v>83.09999999999999</v>
+        <v>53.5</v>
       </c>
       <c r="O58">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P58">
         <v>0</v>
@@ -4225,37 +4225,37 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="G59">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="H59">
-        <v>-1.8</v>
+        <v>-1.3</v>
       </c>
       <c r="I59">
         <v>0</v>
       </c>
       <c r="J59">
-        <v>13.1</v>
+        <v>9.1</v>
       </c>
       <c r="K59">
         <v>40</v>
       </c>
       <c r="L59">
-        <v>53.1</v>
+        <v>49.1</v>
       </c>
       <c r="M59">
         <v>0</v>
       </c>
       <c r="N59">
-        <v>80.59999999999999</v>
+        <v>51.9</v>
       </c>
       <c r="O59">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P59">
         <v>0</v>
@@ -4290,37 +4290,37 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F60">
         <v>0</v>
       </c>
       <c r="G60">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H60">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="I60">
         <v>0</v>
       </c>
       <c r="J60">
-        <v>11.4</v>
+        <v>7.7</v>
       </c>
       <c r="K60">
         <v>40</v>
       </c>
       <c r="L60">
-        <v>51.4</v>
+        <v>47.7</v>
       </c>
       <c r="M60">
         <v>0</v>
       </c>
       <c r="N60">
-        <v>79.3</v>
+        <v>50.4</v>
       </c>
       <c r="O60">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P60">
         <v>0</v>
@@ -4355,37 +4355,37 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="H61">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="I61">
         <v>0</v>
       </c>
       <c r="J61">
-        <v>10.5</v>
+        <v>6.9</v>
       </c>
       <c r="K61">
         <v>40</v>
       </c>
       <c r="L61">
-        <v>50.5</v>
+        <v>46.9</v>
       </c>
       <c r="M61">
         <v>0</v>
       </c>
       <c r="N61">
-        <v>77.59999999999999</v>
+        <v>49.5</v>
       </c>
       <c r="O61">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P61">
         <v>0</v>
@@ -4435,22 +4435,22 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>9.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="K62">
         <v>40</v>
       </c>
       <c r="L62">
-        <v>49.3</v>
+        <v>45.8</v>
       </c>
       <c r="M62">
         <v>0</v>
       </c>
       <c r="N62">
-        <v>75.90000000000001</v>
+        <v>48.2</v>
       </c>
       <c r="O62">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P62">
         <v>0</v>
@@ -4500,22 +4500,22 @@
         <v>0</v>
       </c>
       <c r="J63">
-        <v>8.1</v>
+        <v>4.6</v>
       </c>
       <c r="K63">
         <v>40</v>
       </c>
       <c r="L63">
-        <v>48.1</v>
+        <v>44.6</v>
       </c>
       <c r="M63">
         <v>0</v>
       </c>
       <c r="N63">
-        <v>75</v>
+        <v>46.9</v>
       </c>
       <c r="O63">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P63">
         <v>0</v>
@@ -4565,22 +4565,22 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="K64">
         <v>40</v>
       </c>
       <c r="L64">
-        <v>47.5</v>
+        <v>44</v>
       </c>
       <c r="M64">
         <v>0</v>
       </c>
       <c r="N64">
-        <v>74.59999999999999</v>
+        <v>46.2</v>
       </c>
       <c r="O64">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P64">
         <v>0</v>
@@ -4630,22 +4630,22 @@
         <v>0</v>
       </c>
       <c r="J65">
-        <v>7.2</v>
+        <v>3.7</v>
       </c>
       <c r="K65">
         <v>40</v>
       </c>
       <c r="L65">
-        <v>47.2</v>
+        <v>43.7</v>
       </c>
       <c r="M65">
         <v>0</v>
       </c>
       <c r="N65">
-        <v>74</v>
+        <v>45.9</v>
       </c>
       <c r="O65">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P65">
         <v>0</v>
@@ -4695,22 +4695,22 @@
         <v>0</v>
       </c>
       <c r="J66">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="K66">
         <v>40</v>
       </c>
       <c r="L66">
-        <v>46.8</v>
+        <v>43.3</v>
       </c>
       <c r="M66">
         <v>0</v>
       </c>
       <c r="N66">
-        <v>73.8</v>
+        <v>45.5</v>
       </c>
       <c r="O66">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P66">
         <v>0</v>
@@ -4760,22 +4760,22 @@
         <v>0</v>
       </c>
       <c r="J67">
-        <v>6.7</v>
+        <v>3.2</v>
       </c>
       <c r="K67">
         <v>40</v>
       </c>
       <c r="L67">
-        <v>46.7</v>
+        <v>43.2</v>
       </c>
       <c r="M67">
         <v>0</v>
       </c>
       <c r="N67">
-        <v>72</v>
+        <v>45.3</v>
       </c>
       <c r="O67">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P67">
         <v>0</v>
@@ -4825,22 +4825,22 @@
         <v>0</v>
       </c>
       <c r="J68">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="K68">
         <v>40</v>
       </c>
       <c r="L68">
-        <v>45.5</v>
+        <v>42</v>
       </c>
       <c r="M68">
         <v>0</v>
       </c>
       <c r="N68">
-        <v>70.2</v>
+        <v>44</v>
       </c>
       <c r="O68">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P68">
         <v>0</v>
@@ -4890,22 +4890,22 @@
         <v>0</v>
       </c>
       <c r="J69">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="K69">
         <v>40</v>
       </c>
       <c r="L69">
-        <v>44.3</v>
+        <v>40.8</v>
       </c>
       <c r="M69">
         <v>0</v>
       </c>
       <c r="N69">
-        <v>70</v>
+        <v>42.7</v>
       </c>
       <c r="O69">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P69">
         <v>0</v>
@@ -4955,40 +4955,40 @@
         <v>0</v>
       </c>
       <c r="J70">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="K70">
         <v>40</v>
       </c>
       <c r="L70">
-        <v>44.1</v>
+        <v>40.6</v>
       </c>
       <c r="M70">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="N70">
-        <v>86.40000000000001</v>
+        <v>42.5</v>
       </c>
       <c r="O70">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>0.1097560975609756</v>
       </c>
     </row>
     <row r="71" spans="1:21">
@@ -5017,25 +5017,25 @@
         <v>-6.6</v>
       </c>
       <c r="I71">
-        <v>16.4</v>
+        <v>14.6</v>
       </c>
       <c r="J71">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="K71">
         <v>40</v>
       </c>
       <c r="L71">
-        <v>60.5</v>
+        <v>55.2</v>
       </c>
       <c r="M71">
         <v>0</v>
       </c>
       <c r="N71">
-        <v>84.2</v>
+        <v>58.9</v>
       </c>
       <c r="O71">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P71">
         <v>0</v>
@@ -5082,25 +5082,25 @@
         <v>-6.8</v>
       </c>
       <c r="I72">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J72">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="K72">
         <v>40</v>
       </c>
       <c r="L72">
-        <v>53.9</v>
+        <v>48.6</v>
       </c>
       <c r="M72">
         <v>0</v>
       </c>
       <c r="N72">
-        <v>74.40000000000001</v>
+        <v>51.4</v>
       </c>
       <c r="O72">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P72">
         <v>0</v>
@@ -5132,40 +5132,40 @@
         <v>5.9</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="E73">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G73">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="H73">
-        <v>-3.5</v>
+        <v>-2</v>
       </c>
       <c r="I73">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J73">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="K73">
         <v>40</v>
       </c>
       <c r="L73">
-        <v>47.1</v>
+        <v>41.8</v>
       </c>
       <c r="M73">
         <v>0</v>
       </c>
       <c r="N73">
-        <v>69.3</v>
+        <v>43.8</v>
       </c>
       <c r="O73">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P73">
         <v>0</v>
@@ -5200,10 +5200,10 @@
         <v>0</v>
       </c>
       <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
         <v>1.3</v>
-      </c>
-      <c r="F74">
-        <v>0</v>
       </c>
       <c r="G74">
         <v>1.3</v>
@@ -5215,22 +5215,22 @@
         <v>0</v>
       </c>
       <c r="J74">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="K74">
-        <v>40</v>
+        <v>39.8</v>
       </c>
       <c r="L74">
-        <v>43.6</v>
+        <v>39.8</v>
       </c>
       <c r="M74">
         <v>0</v>
       </c>
       <c r="N74">
-        <v>67.40000000000001</v>
+        <v>41.6</v>
       </c>
       <c r="O74">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P74">
         <v>0</v>
@@ -5265,10 +5265,10 @@
         <v>0</v>
       </c>
       <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
         <v>1.2</v>
-      </c>
-      <c r="F75">
-        <v>0</v>
       </c>
       <c r="G75">
         <v>1.2</v>
@@ -5280,22 +5280,22 @@
         <v>0</v>
       </c>
       <c r="J75">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="K75">
-        <v>40</v>
+        <v>38.5</v>
       </c>
       <c r="L75">
-        <v>42.3</v>
+        <v>38.5</v>
       </c>
       <c r="M75">
         <v>0</v>
       </c>
       <c r="N75">
-        <v>65.7</v>
+        <v>40.2</v>
       </c>
       <c r="O75">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P75">
         <v>0</v>
@@ -5330,10 +5330,10 @@
         <v>0</v>
       </c>
       <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
         <v>1.2</v>
-      </c>
-      <c r="F76">
-        <v>0</v>
       </c>
       <c r="G76">
         <v>1.2</v>
@@ -5345,22 +5345,22 @@
         <v>0</v>
       </c>
       <c r="J76">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K76">
-        <v>40</v>
+        <v>37.4</v>
       </c>
       <c r="L76">
-        <v>41.2</v>
+        <v>37.4</v>
       </c>
       <c r="M76">
         <v>0</v>
       </c>
       <c r="N76">
-        <v>63.8</v>
+        <v>38.9</v>
       </c>
       <c r="O76">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P76">
         <v>0</v>
@@ -5413,16 +5413,16 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>40</v>
+        <v>36.2</v>
       </c>
       <c r="L77">
-        <v>40</v>
+        <v>36.2</v>
       </c>
       <c r="M77">
         <v>0</v>
       </c>
       <c r="N77">
-        <v>62.4</v>
+        <v>37.6</v>
       </c>
       <c r="O77">
         <v>0.1</v>
@@ -5478,16 +5478,16 @@
         <v>0</v>
       </c>
       <c r="K78">
-        <v>39</v>
+        <v>35.2</v>
       </c>
       <c r="L78">
-        <v>39</v>
+        <v>35.2</v>
       </c>
       <c r="M78">
         <v>0</v>
       </c>
       <c r="N78">
-        <v>62</v>
+        <v>36.6</v>
       </c>
       <c r="O78">
         <v>0.1</v>
@@ -5543,16 +5543,16 @@
         <v>0</v>
       </c>
       <c r="K79">
-        <v>38.7</v>
+        <v>34.9</v>
       </c>
       <c r="L79">
-        <v>38.7</v>
+        <v>34.9</v>
       </c>
       <c r="M79">
         <v>0</v>
       </c>
       <c r="N79">
-        <v>60.4</v>
+        <v>36.3</v>
       </c>
       <c r="O79">
         <v>0.1</v>
@@ -5608,16 +5608,16 @@
         <v>0</v>
       </c>
       <c r="K80">
-        <v>37.7</v>
+        <v>33.9</v>
       </c>
       <c r="L80">
-        <v>37.7</v>
+        <v>33.9</v>
       </c>
       <c r="M80">
         <v>0</v>
       </c>
       <c r="N80">
-        <v>58.6</v>
+        <v>35.1</v>
       </c>
       <c r="O80">
         <v>0.1</v>
@@ -5673,16 +5673,16 @@
         <v>0</v>
       </c>
       <c r="K81">
-        <v>36.5</v>
+        <v>32.7</v>
       </c>
       <c r="L81">
-        <v>36.5</v>
+        <v>32.7</v>
       </c>
       <c r="M81">
         <v>0</v>
       </c>
       <c r="N81">
-        <v>57</v>
+        <v>33.8</v>
       </c>
       <c r="O81">
         <v>0.1</v>
@@ -5738,16 +5738,16 @@
         <v>0</v>
       </c>
       <c r="K82">
-        <v>35.4</v>
+        <v>31.6</v>
       </c>
       <c r="L82">
-        <v>35.4</v>
+        <v>31.6</v>
       </c>
       <c r="M82">
         <v>0</v>
       </c>
       <c r="N82">
-        <v>55.1</v>
+        <v>32.7</v>
       </c>
       <c r="O82">
         <v>0.1</v>
@@ -5803,16 +5803,16 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <v>34.2</v>
+        <v>30.4</v>
       </c>
       <c r="L83">
-        <v>34.2</v>
+        <v>30.4</v>
       </c>
       <c r="M83">
         <v>0</v>
       </c>
       <c r="N83">
-        <v>53.5</v>
+        <v>31.4</v>
       </c>
       <c r="O83">
         <v>0.1</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="K84">
-        <v>33.1</v>
+        <v>29.3</v>
       </c>
       <c r="L84">
-        <v>33.1</v>
+        <v>29.3</v>
       </c>
       <c r="M84">
         <v>0</v>
       </c>
       <c r="N84">
-        <v>51.8</v>
+        <v>30.2</v>
       </c>
       <c r="O84">
         <v>0.1</v>
@@ -5933,16 +5933,16 @@
         <v>0</v>
       </c>
       <c r="K85">
-        <v>32</v>
+        <v>28.2</v>
       </c>
       <c r="L85">
-        <v>32</v>
+        <v>28.2</v>
       </c>
       <c r="M85">
         <v>0</v>
       </c>
       <c r="N85">
-        <v>51.6</v>
+        <v>29.1</v>
       </c>
       <c r="O85">
         <v>0.1</v>
@@ -5998,16 +5998,16 @@
         <v>0</v>
       </c>
       <c r="K86">
-        <v>31.9</v>
+        <v>28.1</v>
       </c>
       <c r="L86">
-        <v>31.9</v>
+        <v>28.1</v>
       </c>
       <c r="M86">
         <v>0</v>
       </c>
       <c r="N86">
-        <v>50.9</v>
+        <v>28.9</v>
       </c>
       <c r="O86">
         <v>0.1</v>
@@ -6063,16 +6063,16 @@
         <v>0</v>
       </c>
       <c r="K87">
-        <v>31.5</v>
+        <v>27.7</v>
       </c>
       <c r="L87">
-        <v>31.5</v>
+        <v>27.7</v>
       </c>
       <c r="M87">
         <v>0</v>
       </c>
       <c r="N87">
-        <v>49.1</v>
+        <v>28.5</v>
       </c>
       <c r="O87">
         <v>0.1</v>
@@ -6128,16 +6128,16 @@
         <v>0</v>
       </c>
       <c r="K88">
-        <v>30.3</v>
+        <v>26.5</v>
       </c>
       <c r="L88">
-        <v>30.3</v>
+        <v>26.5</v>
       </c>
       <c r="M88">
         <v>0</v>
       </c>
       <c r="N88">
-        <v>48</v>
+        <v>27.2</v>
       </c>
       <c r="O88">
         <v>0.1</v>
@@ -6193,16 +6193,16 @@
         <v>0</v>
       </c>
       <c r="K89">
-        <v>29.6</v>
+        <v>25.8</v>
       </c>
       <c r="L89">
-        <v>29.6</v>
+        <v>25.8</v>
       </c>
       <c r="M89">
         <v>0</v>
       </c>
       <c r="N89">
-        <v>46.5</v>
+        <v>26.5</v>
       </c>
       <c r="O89">
         <v>0.1</v>
@@ -6258,37 +6258,37 @@
         <v>0</v>
       </c>
       <c r="K90">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L90">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="M90">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N90">
-        <v>53</v>
+        <v>25.5</v>
       </c>
       <c r="O90">
         <v>0.1</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>0.06153846153846154</v>
       </c>
     </row>
     <row r="91" spans="1:21">
@@ -6317,43 +6317,43 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I91">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="J91">
         <v>0</v>
       </c>
       <c r="K91">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L91">
-        <v>35.1</v>
+        <v>30.9</v>
       </c>
       <c r="M91">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="N91">
-        <v>61.3</v>
+        <v>32</v>
       </c>
       <c r="O91">
         <v>0.1</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>0.07228915662650602</v>
       </c>
     </row>
     <row r="92" spans="1:21">
@@ -6382,43 +6382,43 @@
         <v>12.8</v>
       </c>
       <c r="I92">
-        <v>14.8</v>
+        <v>13.8</v>
       </c>
       <c r="J92">
         <v>0</v>
       </c>
       <c r="K92">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L92">
-        <v>43.4</v>
+        <v>38.6</v>
       </c>
       <c r="M92">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="N92">
-        <v>74.09999999999999</v>
+        <v>40.3</v>
       </c>
       <c r="O92">
         <v>0.1</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>0.1015625</v>
       </c>
     </row>
     <row r="93" spans="1:21">
@@ -6450,22 +6450,22 @@
         <v>20</v>
       </c>
       <c r="J93">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="K93">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L93">
-        <v>56.2</v>
+        <v>50.1</v>
       </c>
       <c r="M93">
         <v>0</v>
       </c>
       <c r="N93">
-        <v>80</v>
+        <v>53.1</v>
       </c>
       <c r="O93">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P93">
         <v>0</v>
@@ -6515,22 +6515,22 @@
         <v>14.8</v>
       </c>
       <c r="J94">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="K94">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L94">
-        <v>51</v>
+        <v>44.9</v>
       </c>
       <c r="M94">
         <v>0</v>
       </c>
       <c r="N94">
-        <v>72.40000000000001</v>
+        <v>47.2</v>
       </c>
       <c r="O94">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P94">
         <v>0</v>
@@ -6580,22 +6580,22 @@
         <v>9.5</v>
       </c>
       <c r="J95">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="K95">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L95">
-        <v>45.7</v>
+        <v>39.6</v>
       </c>
       <c r="M95">
         <v>0</v>
       </c>
       <c r="N95">
-        <v>65.3</v>
+        <v>41.4</v>
       </c>
       <c r="O95">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P95">
         <v>0</v>
@@ -6645,22 +6645,22 @@
         <v>4.7</v>
       </c>
       <c r="J96">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="K96">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L96">
-        <v>40.9</v>
+        <v>34.8</v>
       </c>
       <c r="M96">
         <v>0</v>
       </c>
       <c r="N96">
-        <v>60.8</v>
+        <v>36.1</v>
       </c>
       <c r="O96">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P96">
         <v>0</v>
@@ -6710,40 +6710,40 @@
         <v>1.7</v>
       </c>
       <c r="J97">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="K97">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L97">
-        <v>37.9</v>
+        <v>31.8</v>
       </c>
       <c r="M97">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N97">
-        <v>67.09999999999999</v>
+        <v>32.9</v>
       </c>
       <c r="O97">
         <v>0.1</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>0.07936507936507936</v>
       </c>
     </row>
     <row r="98" spans="1:21">
@@ -6772,43 +6772,43 @@
         <v>20.3</v>
       </c>
       <c r="I98">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J98">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="K98">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L98">
-        <v>44.2</v>
+        <v>37.6</v>
       </c>
       <c r="M98">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="N98">
-        <v>87.40000000000001</v>
+        <v>39.2</v>
       </c>
       <c r="O98">
+        <v>0.1</v>
+      </c>
+      <c r="P98">
+        <v>1.9</v>
+      </c>
+      <c r="Q98">
+        <v>0.3</v>
+      </c>
+      <c r="R98">
+        <v>0.5</v>
+      </c>
+      <c r="S98">
         <v>0.2</v>
       </c>
-      <c r="P98">
-        <v>0</v>
-      </c>
-      <c r="Q98">
-        <v>0</v>
-      </c>
-      <c r="R98">
-        <v>0</v>
-      </c>
-      <c r="S98">
-        <v>0</v>
-      </c>
       <c r="T98">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>0.1083743842364532</v>
       </c>
     </row>
     <row r="99" spans="1:21">
@@ -6840,40 +6840,40 @@
         <v>20</v>
       </c>
       <c r="J99">
-        <v>15.9</v>
+        <v>10.9</v>
       </c>
       <c r="K99">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L99">
-        <v>64.5</v>
+        <v>55.7</v>
       </c>
       <c r="M99">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N99">
-        <v>88.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="O99">
+        <v>0.1</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
         <v>0.2</v>
       </c>
-      <c r="P99">
-        <v>0</v>
-      </c>
-      <c r="Q99">
-        <v>0</v>
-      </c>
       <c r="R99">
         <v>0</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>0.1333333333333333</v>
       </c>
     </row>
     <row r="100" spans="1:21">
@@ -6905,22 +6905,22 @@
         <v>20</v>
       </c>
       <c r="J100">
-        <v>17.4</v>
+        <v>12.2</v>
       </c>
       <c r="K100">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L100">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="M100">
         <v>0</v>
       </c>
       <c r="N100">
-        <v>95.90000000000001</v>
+        <v>61</v>
       </c>
       <c r="O100">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P100">
         <v>0</v>
@@ -6970,22 +6970,22 @@
         <v>16.4</v>
       </c>
       <c r="J101">
-        <v>17.4</v>
+        <v>12.2</v>
       </c>
       <c r="K101">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L101">
-        <v>62.4</v>
+        <v>53.4</v>
       </c>
       <c r="M101">
         <v>0</v>
       </c>
       <c r="N101">
-        <v>92.40000000000001</v>
+        <v>56.9</v>
       </c>
       <c r="O101">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P101">
         <v>0</v>
@@ -7035,22 +7035,22 @@
         <v>13.8</v>
       </c>
       <c r="J102">
-        <v>17.4</v>
+        <v>12.2</v>
       </c>
       <c r="K102">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L102">
-        <v>59.8</v>
+        <v>50.8</v>
       </c>
       <c r="M102">
         <v>0</v>
       </c>
       <c r="N102">
-        <v>89.59999999999999</v>
+        <v>53.9</v>
       </c>
       <c r="O102">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P102">
         <v>0</v>
@@ -7100,40 +7100,40 @@
         <v>11.8</v>
       </c>
       <c r="J103">
-        <v>17.4</v>
+        <v>12.2</v>
       </c>
       <c r="K103">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L103">
-        <v>57.8</v>
+        <v>48.8</v>
       </c>
       <c r="M103">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="N103">
-        <v>95.5</v>
+        <v>51.6</v>
       </c>
       <c r="O103">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R103">
         <v>0</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>0.1186440677966102</v>
       </c>
     </row>
     <row r="104" spans="1:21">
@@ -7162,43 +7162,43 @@
         <v>1.6</v>
       </c>
       <c r="I104">
-        <v>17.7</v>
+        <v>17</v>
       </c>
       <c r="J104">
-        <v>17.4</v>
+        <v>12.2</v>
       </c>
       <c r="K104">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L104">
-        <v>63.7</v>
+        <v>54</v>
       </c>
       <c r="M104">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N104">
-        <v>97.09999999999999</v>
+        <v>57.5</v>
       </c>
       <c r="O104">
+        <v>0.1</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="Q104">
         <v>0.2</v>
       </c>
-      <c r="P104">
-        <v>0</v>
-      </c>
-      <c r="Q104">
-        <v>0</v>
-      </c>
       <c r="R104">
         <v>0</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="105" spans="1:21">
@@ -7227,43 +7227,43 @@
         <v>5.7</v>
       </c>
       <c r="I105">
-        <v>19.3</v>
+        <v>18.4</v>
       </c>
       <c r="J105">
-        <v>17.4</v>
+        <v>12.2</v>
       </c>
       <c r="K105">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L105">
-        <v>65.3</v>
+        <v>55.4</v>
       </c>
       <c r="M105">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N105">
-        <v>102.8</v>
+        <v>59.1</v>
       </c>
       <c r="O105">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R105">
         <v>0</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>0.1403508771929824</v>
       </c>
     </row>
     <row r="106" spans="1:21">
@@ -7295,22 +7295,22 @@
         <v>20</v>
       </c>
       <c r="J106">
-        <v>22.4</v>
+        <v>15.5</v>
       </c>
       <c r="K106">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L106">
-        <v>71</v>
+        <v>60.3</v>
       </c>
       <c r="M106">
         <v>0</v>
       </c>
       <c r="N106">
-        <v>105.8</v>
+        <v>64.8</v>
       </c>
       <c r="O106">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="P106">
         <v>0</v>
@@ -7360,22 +7360,22 @@
         <v>18.8</v>
       </c>
       <c r="J107">
-        <v>22.4</v>
+        <v>15.5</v>
       </c>
       <c r="K107">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L107">
-        <v>69.8</v>
+        <v>59.1</v>
       </c>
       <c r="M107">
         <v>0</v>
       </c>
       <c r="N107">
-        <v>102.1</v>
+        <v>63.4</v>
       </c>
       <c r="O107">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="P107">
         <v>0</v>
@@ -7425,22 +7425,22 @@
         <v>16</v>
       </c>
       <c r="J108">
-        <v>22.4</v>
+        <v>15.5</v>
       </c>
       <c r="K108">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L108">
-        <v>67</v>
+        <v>56.3</v>
       </c>
       <c r="M108">
         <v>0</v>
       </c>
       <c r="N108">
-        <v>96.8</v>
+        <v>60.2</v>
       </c>
       <c r="O108">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="P108">
         <v>0</v>
@@ -7490,22 +7490,22 @@
         <v>12</v>
       </c>
       <c r="J109">
-        <v>22.4</v>
+        <v>15.5</v>
       </c>
       <c r="K109">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L109">
-        <v>63</v>
+        <v>52.3</v>
       </c>
       <c r="M109">
         <v>0</v>
       </c>
       <c r="N109">
-        <v>89.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="O109">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="P109">
         <v>0</v>
@@ -7555,22 +7555,22 @@
         <v>6.8</v>
       </c>
       <c r="J110">
-        <v>22.4</v>
+        <v>15.5</v>
       </c>
       <c r="K110">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L110">
-        <v>57.8</v>
+        <v>47.1</v>
       </c>
       <c r="M110">
         <v>0</v>
       </c>
       <c r="N110">
-        <v>82.59999999999999</v>
+        <v>49.7</v>
       </c>
       <c r="O110">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P110">
         <v>0</v>
@@ -7620,22 +7620,22 @@
         <v>1.8</v>
       </c>
       <c r="J111">
-        <v>22.4</v>
+        <v>15.5</v>
       </c>
       <c r="K111">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L111">
-        <v>52.8</v>
+        <v>42.1</v>
       </c>
       <c r="M111">
         <v>0</v>
       </c>
       <c r="N111">
-        <v>82.59999999999999</v>
+        <v>49.7</v>
       </c>
       <c r="O111">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P111">
         <v>0</v>
@@ -7685,40 +7685,40 @@
         <v>1.8</v>
       </c>
       <c r="J112">
-        <v>22.4</v>
+        <v>15.5</v>
       </c>
       <c r="K112">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L112">
-        <v>52.8</v>
+        <v>42.1</v>
       </c>
       <c r="M112">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N112">
-        <v>105.8</v>
+        <v>44.1</v>
       </c>
       <c r="O112">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="113" spans="1:21">
@@ -7750,40 +7750,40 @@
         <v>20</v>
       </c>
       <c r="J113">
-        <v>27.4</v>
+        <v>17.6</v>
       </c>
       <c r="K113">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L113">
-        <v>76</v>
+        <v>62.4</v>
       </c>
       <c r="M113">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N113">
-        <v>108.8</v>
+        <v>67.3</v>
       </c>
       <c r="O113">
+        <v>0.1</v>
+      </c>
+      <c r="P113">
+        <v>0.1</v>
+      </c>
+      <c r="Q113">
+        <v>0.4</v>
+      </c>
+      <c r="R113">
+        <v>0.1</v>
+      </c>
+      <c r="S113">
         <v>0.3</v>
       </c>
-      <c r="P113">
-        <v>0</v>
-      </c>
-      <c r="Q113">
-        <v>0</v>
-      </c>
-      <c r="R113">
-        <v>0</v>
-      </c>
-      <c r="S113">
-        <v>0</v>
-      </c>
       <c r="T113">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="114" spans="1:21">
@@ -7815,22 +7815,22 @@
         <v>20</v>
       </c>
       <c r="J114">
-        <v>30.4</v>
+        <v>20.1</v>
       </c>
       <c r="K114">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L114">
-        <v>79</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="M114">
         <v>0</v>
       </c>
       <c r="N114">
-        <v>116.2</v>
+        <v>70.3</v>
       </c>
       <c r="O114">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P114">
         <v>0</v>
@@ -7880,40 +7880,40 @@
         <v>19</v>
       </c>
       <c r="J115">
-        <v>30.4</v>
+        <v>20.1</v>
       </c>
       <c r="K115">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L115">
-        <v>78</v>
+        <v>63.9</v>
       </c>
       <c r="M115">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N115">
-        <v>121.1</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="O115">
+        <v>0.2</v>
+      </c>
+      <c r="P115">
+        <v>0.4</v>
+      </c>
+      <c r="Q115">
+        <v>0.4</v>
+      </c>
+      <c r="R115">
+        <v>0.1</v>
+      </c>
+      <c r="S115">
         <v>0.3</v>
       </c>
-      <c r="P115">
-        <v>0</v>
-      </c>
-      <c r="Q115">
-        <v>0</v>
-      </c>
-      <c r="R115">
-        <v>0</v>
-      </c>
-      <c r="S115">
-        <v>0</v>
-      </c>
       <c r="T115">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>0.163265306122449</v>
       </c>
     </row>
     <row r="116" spans="1:21">
@@ -7945,40 +7945,40 @@
         <v>20</v>
       </c>
       <c r="J116">
-        <v>34.3</v>
+        <v>23.2</v>
       </c>
       <c r="K116">
-        <v>28.6</v>
+        <v>24.8</v>
       </c>
       <c r="L116">
-        <v>82.90000000000001</v>
+        <v>68</v>
       </c>
       <c r="M116">
-        <v>31.6</v>
+        <v>21.6</v>
       </c>
       <c r="N116">
-        <v>121.1</v>
+        <v>74</v>
       </c>
       <c r="O116">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P116">
-        <v>30.5</v>
+        <v>20.8</v>
       </c>
       <c r="Q116">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="R116">
-        <v>10.2</v>
+        <v>5.6</v>
       </c>
       <c r="S116">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="T116">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="U116">
-        <v>0.4599708879184862</v>
+        <v>0.314410480349345</v>
       </c>
     </row>
     <row r="117" spans="1:21">
@@ -8013,19 +8013,19 @@
         <v>60</v>
       </c>
       <c r="K117">
-        <v>40</v>
+        <v>35.1</v>
       </c>
       <c r="L117">
-        <v>120</v>
+        <v>115.1</v>
       </c>
       <c r="M117">
         <v>0</v>
       </c>
       <c r="N117">
-        <v>155.2</v>
+        <v>142.7</v>
       </c>
       <c r="O117">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P117">
         <v>0</v>
@@ -8078,19 +8078,19 @@
         <v>60</v>
       </c>
       <c r="K118">
-        <v>40</v>
+        <v>35.1</v>
       </c>
       <c r="L118">
-        <v>118</v>
+        <v>113.1</v>
       </c>
       <c r="M118">
         <v>0</v>
       </c>
       <c r="N118">
-        <v>153.4</v>
+        <v>138.7</v>
       </c>
       <c r="O118">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="P118">
         <v>0</v>
@@ -8143,19 +8143,19 @@
         <v>60</v>
       </c>
       <c r="K119">
-        <v>40</v>
+        <v>35.1</v>
       </c>
       <c r="L119">
-        <v>114.9</v>
+        <v>110</v>
       </c>
       <c r="M119">
         <v>0</v>
       </c>
       <c r="N119">
-        <v>151.5</v>
+        <v>133</v>
       </c>
       <c r="O119">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="P119">
         <v>0</v>
@@ -8208,19 +8208,19 @@
         <v>60</v>
       </c>
       <c r="K120">
-        <v>40</v>
+        <v>35.1</v>
       </c>
       <c r="L120">
-        <v>112.1</v>
+        <v>107.2</v>
       </c>
       <c r="M120">
         <v>0</v>
       </c>
       <c r="N120">
-        <v>148.4</v>
+        <v>128.1</v>
       </c>
       <c r="O120">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="P120">
         <v>0</v>
@@ -8273,19 +8273,19 @@
         <v>60</v>
       </c>
       <c r="K121">
-        <v>40</v>
+        <v>35.1</v>
       </c>
       <c r="L121">
-        <v>108.2</v>
+        <v>103.3</v>
       </c>
       <c r="M121">
         <v>0</v>
       </c>
       <c r="N121">
-        <v>145.9</v>
+        <v>121.8</v>
       </c>
       <c r="O121">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="P121">
         <v>0</v>
@@ -8338,37 +8338,37 @@
         <v>60</v>
       </c>
       <c r="K122">
-        <v>40</v>
+        <v>35.1</v>
       </c>
       <c r="L122">
-        <v>105.4</v>
+        <v>100.5</v>
       </c>
       <c r="M122">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N122">
-        <v>148.1</v>
+        <v>117.5</v>
       </c>
       <c r="O122">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="P122">
         <v>0</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="123" spans="1:21">
@@ -8397,43 +8397,43 @@
         <v>18.1</v>
       </c>
       <c r="I123">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J123">
         <v>60</v>
       </c>
       <c r="K123">
-        <v>40</v>
+        <v>35.1</v>
       </c>
       <c r="L123">
-        <v>107.6</v>
+        <v>102</v>
       </c>
       <c r="M123">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="N123">
-        <v>148.1</v>
+        <v>119.7</v>
       </c>
       <c r="O123">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="P123">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="Q123">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="R123">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="S123">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="T123">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="U123">
-        <v>0.3149171270718232</v>
+        <v>0.4088397790055249</v>
       </c>
     </row>
     <row r="124" spans="1:21">
@@ -8462,34 +8462,34 @@
         <v>5.8</v>
       </c>
       <c r="I124">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="J124">
         <v>60</v>
       </c>
       <c r="K124">
-        <v>40</v>
+        <v>35.1</v>
       </c>
       <c r="L124">
-        <v>120</v>
+        <v>112.6</v>
       </c>
       <c r="M124">
-        <v>6.2</v>
+        <v>2.9</v>
       </c>
       <c r="N124">
-        <v>153.9</v>
+        <v>137.8</v>
       </c>
       <c r="O124">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="P124">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="Q124">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="R124">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="S124">
         <v>0.9</v>
@@ -8498,7 +8498,7 @@
         <v>0.9</v>
       </c>
       <c r="U124">
-        <v>1.068965517241379</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="125" spans="1:21">
@@ -8527,31 +8527,31 @@
         <v>7.6</v>
       </c>
       <c r="I125">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="J125">
         <v>60</v>
       </c>
       <c r="K125">
-        <v>40</v>
+        <v>35.5</v>
       </c>
       <c r="L125">
-        <v>119.6</v>
+        <v>115.5</v>
       </c>
       <c r="M125">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="N125">
-        <v>153.9</v>
+        <v>143.6</v>
       </c>
       <c r="O125">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="P125">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="Q125">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="R125">
         <v>0.4</v>
@@ -8563,7 +8563,7 @@
         <v>0.9</v>
       </c>
       <c r="U125">
-        <v>0.9473684210526316</v>
+        <v>0.5789473684210527</v>
       </c>
     </row>
     <row r="126" spans="1:21">
@@ -8598,25 +8598,25 @@
         <v>60</v>
       </c>
       <c r="K126">
-        <v>40</v>
+        <v>38.7</v>
       </c>
       <c r="L126">
-        <v>120</v>
+        <v>118.7</v>
       </c>
       <c r="M126">
-        <v>22.9</v>
+        <v>21.6</v>
       </c>
       <c r="N126">
-        <v>153.9</v>
+        <v>151.2</v>
       </c>
       <c r="O126">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="P126">
-        <v>20.4</v>
+        <v>19.2</v>
       </c>
       <c r="Q126">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R126">
         <v>2.3</v>
@@ -8628,7 +8628,7 @@
         <v>0.9</v>
       </c>
       <c r="U126">
-        <v>1</v>
+        <v>0.943231441048035</v>
       </c>
     </row>
     <row r="127" spans="1:21">
@@ -8669,31 +8669,31 @@
         <v>120</v>
       </c>
       <c r="M127">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="N127">
-        <v>154.9</v>
+        <v>156</v>
       </c>
       <c r="O127">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="P127">
         <v>0</v>
       </c>
       <c r="Q127">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="R127">
         <v>0</v>
       </c>
       <c r="S127">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="T127">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="U127">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:21">
@@ -8722,7 +8722,7 @@
         <v>-3</v>
       </c>
       <c r="I128">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="J128">
         <v>60</v>
@@ -8731,16 +8731,16 @@
         <v>40</v>
       </c>
       <c r="L128">
-        <v>119.8</v>
+        <v>120</v>
       </c>
       <c r="M128">
         <v>0</v>
       </c>
       <c r="N128">
-        <v>154.6</v>
+        <v>156</v>
       </c>
       <c r="O128">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="P128">
         <v>0</v>
@@ -8787,7 +8787,7 @@
         <v>-4</v>
       </c>
       <c r="I129">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="J129">
         <v>60</v>
@@ -8796,16 +8796,16 @@
         <v>40</v>
       </c>
       <c r="L129">
-        <v>116.8</v>
+        <v>117</v>
       </c>
       <c r="M129">
         <v>0</v>
       </c>
       <c r="N129">
-        <v>152</v>
+        <v>146.9</v>
       </c>
       <c r="O129">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="P129">
         <v>0</v>
@@ -8852,7 +8852,7 @@
         <v>-3.2</v>
       </c>
       <c r="I130">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="J130">
         <v>60</v>
@@ -8861,16 +8861,16 @@
         <v>40</v>
       </c>
       <c r="L130">
-        <v>112.8</v>
+        <v>113</v>
       </c>
       <c r="M130">
         <v>0</v>
       </c>
       <c r="N130">
-        <v>149.5</v>
+        <v>138.5</v>
       </c>
       <c r="O130">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="P130">
         <v>0</v>
@@ -8917,7 +8917,7 @@
         <v>1.8</v>
       </c>
       <c r="I131">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J131">
         <v>60</v>
@@ -8926,34 +8926,34 @@
         <v>40</v>
       </c>
       <c r="L131">
-        <v>109.6</v>
+        <v>109.8</v>
       </c>
       <c r="M131">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N131">
-        <v>151.3</v>
+        <v>132.6</v>
       </c>
       <c r="O131">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="P131">
         <v>0</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="R131">
         <v>0</v>
       </c>
       <c r="S131">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="T131">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="U131">
-        <v>0</v>
+        <v>0.4444444444444445</v>
       </c>
     </row>
     <row r="132" spans="1:21">
@@ -8982,7 +8982,7 @@
         <v>-1.9</v>
       </c>
       <c r="I132">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="J132">
         <v>60</v>
@@ -8991,16 +8991,16 @@
         <v>40</v>
       </c>
       <c r="L132">
-        <v>111.4</v>
+        <v>110.8</v>
       </c>
       <c r="M132">
         <v>0</v>
       </c>
       <c r="N132">
-        <v>149.4</v>
+        <v>134.4</v>
       </c>
       <c r="O132">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="P132">
         <v>0</v>
@@ -9047,7 +9047,7 @@
         <v>-4.3</v>
       </c>
       <c r="I133">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="J133">
         <v>60</v>
@@ -9056,16 +9056,16 @@
         <v>40</v>
       </c>
       <c r="L133">
-        <v>109.5</v>
+        <v>108.9</v>
       </c>
       <c r="M133">
         <v>0</v>
       </c>
       <c r="N133">
-        <v>145.7</v>
+        <v>131</v>
       </c>
       <c r="O133">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="P133">
         <v>0</v>
@@ -9112,7 +9112,7 @@
         <v>-4.2</v>
       </c>
       <c r="I134">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J134">
         <v>60</v>
@@ -9121,16 +9121,16 @@
         <v>40</v>
       </c>
       <c r="L134">
-        <v>105.2</v>
+        <v>104.6</v>
       </c>
       <c r="M134">
         <v>0</v>
       </c>
       <c r="N134">
-        <v>141.8</v>
+        <v>123.9</v>
       </c>
       <c r="O134">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="P134">
         <v>0</v>
@@ -9162,10 +9162,10 @@
         <v>2.8</v>
       </c>
       <c r="D135">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="E135">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -9177,7 +9177,7 @@
         <v>-2.8</v>
       </c>
       <c r="I135">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J135">
         <v>60</v>
@@ -9186,16 +9186,16 @@
         <v>40</v>
       </c>
       <c r="L135">
-        <v>101</v>
+        <v>100.4</v>
       </c>
       <c r="M135">
         <v>0</v>
       </c>
       <c r="N135">
-        <v>139</v>
+        <v>117.3</v>
       </c>
       <c r="O135">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="P135">
         <v>0</v>
@@ -9245,22 +9245,22 @@
         <v>0</v>
       </c>
       <c r="J136">
-        <v>58.2</v>
+        <v>57.6</v>
       </c>
       <c r="K136">
         <v>40</v>
       </c>
       <c r="L136">
-        <v>98.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M136">
         <v>0</v>
       </c>
       <c r="N136">
-        <v>136.3</v>
+        <v>113.1</v>
       </c>
       <c r="O136">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="P136">
         <v>0</v>
@@ -9310,22 +9310,22 @@
         <v>0</v>
       </c>
       <c r="J137">
-        <v>55.6</v>
+        <v>55</v>
       </c>
       <c r="K137">
         <v>40</v>
       </c>
       <c r="L137">
-        <v>95.59999999999999</v>
+        <v>95</v>
       </c>
       <c r="M137">
         <v>0</v>
       </c>
       <c r="N137">
-        <v>133.6</v>
+        <v>109.3</v>
       </c>
       <c r="O137">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="P137">
         <v>0</v>
@@ -9360,37 +9360,37 @@
         <v>0</v>
       </c>
       <c r="E138">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F138">
         <v>0</v>
       </c>
       <c r="G138">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H138">
-        <v>-1.8</v>
+        <v>-1.7</v>
       </c>
       <c r="I138">
         <v>0</v>
       </c>
       <c r="J138">
-        <v>53</v>
+        <v>52.4</v>
       </c>
       <c r="K138">
         <v>40</v>
       </c>
       <c r="L138">
-        <v>93</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="M138">
         <v>0</v>
       </c>
       <c r="N138">
-        <v>131.6</v>
+        <v>105.7</v>
       </c>
       <c r="O138">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="P138">
         <v>0</v>
@@ -9440,22 +9440,22 @@
         <v>0</v>
       </c>
       <c r="J139">
-        <v>51.2</v>
+        <v>50.7</v>
       </c>
       <c r="K139">
         <v>40</v>
       </c>
       <c r="L139">
-        <v>91.2</v>
+        <v>90.7</v>
       </c>
       <c r="M139">
         <v>0</v>
       </c>
       <c r="N139">
-        <v>129.4</v>
+        <v>103.3</v>
       </c>
       <c r="O139">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="P139">
         <v>0</v>
@@ -9505,22 +9505,22 @@
         <v>0</v>
       </c>
       <c r="J140">
-        <v>49.2</v>
+        <v>48.7</v>
       </c>
       <c r="K140">
         <v>40</v>
       </c>
       <c r="L140">
-        <v>89.2</v>
+        <v>88.7</v>
       </c>
       <c r="M140">
         <v>0</v>
       </c>
       <c r="N140">
-        <v>126.9</v>
+        <v>100.5</v>
       </c>
       <c r="O140">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="P140">
         <v>0</v>
@@ -9570,22 +9570,22 @@
         <v>0</v>
       </c>
       <c r="J141">
-        <v>47.1</v>
+        <v>46.6</v>
       </c>
       <c r="K141">
         <v>40</v>
       </c>
       <c r="L141">
-        <v>87.09999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="M141">
         <v>0</v>
       </c>
       <c r="N141">
-        <v>124.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O141">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="P141">
         <v>0</v>
@@ -9620,37 +9620,37 @@
         <v>0</v>
       </c>
       <c r="E142">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F142">
         <v>0</v>
       </c>
       <c r="G142">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="H142">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="I142">
         <v>0</v>
       </c>
       <c r="J142">
-        <v>45.2</v>
+        <v>44.8</v>
       </c>
       <c r="K142">
         <v>40</v>
       </c>
       <c r="L142">
-        <v>85.2</v>
+        <v>84.8</v>
       </c>
       <c r="M142">
         <v>0</v>
       </c>
       <c r="N142">
-        <v>122.9</v>
+        <v>95.2</v>
       </c>
       <c r="O142">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="P142">
         <v>0</v>
@@ -9700,22 +9700,22 @@
         <v>0</v>
       </c>
       <c r="J143">
-        <v>43.6</v>
+        <v>43.1</v>
       </c>
       <c r="K143">
         <v>40</v>
       </c>
       <c r="L143">
-        <v>83.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="M143">
         <v>0</v>
       </c>
       <c r="N143">
-        <v>121</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="O143">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P143">
         <v>0</v>
@@ -9765,22 +9765,22 @@
         <v>0</v>
       </c>
       <c r="J144">
-        <v>42</v>
+        <v>41.6</v>
       </c>
       <c r="K144">
         <v>40</v>
       </c>
       <c r="L144">
-        <v>82</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="M144">
         <v>0</v>
       </c>
       <c r="N144">
-        <v>118.9</v>
+        <v>91</v>
       </c>
       <c r="O144">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P144">
         <v>0</v>
@@ -9830,22 +9830,22 @@
         <v>0</v>
       </c>
       <c r="J145">
-        <v>40.2</v>
+        <v>39.8</v>
       </c>
       <c r="K145">
         <v>40</v>
       </c>
       <c r="L145">
-        <v>80.2</v>
+        <v>79.8</v>
       </c>
       <c r="M145">
         <v>0</v>
       </c>
       <c r="N145">
-        <v>117.1</v>
+        <v>88.8</v>
       </c>
       <c r="O145">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P145">
         <v>0</v>
@@ -9895,22 +9895,22 @@
         <v>0</v>
       </c>
       <c r="J146">
-        <v>38.8</v>
+        <v>38.4</v>
       </c>
       <c r="K146">
         <v>40</v>
       </c>
       <c r="L146">
-        <v>78.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="M146">
         <v>0</v>
       </c>
       <c r="N146">
-        <v>115.6</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="O146">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P146">
         <v>0</v>
@@ -9960,22 +9960,22 @@
         <v>0</v>
       </c>
       <c r="J147">
-        <v>37.5</v>
+        <v>37.1</v>
       </c>
       <c r="K147">
         <v>40</v>
       </c>
       <c r="L147">
-        <v>77.5</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="M147">
         <v>0</v>
       </c>
       <c r="N147">
-        <v>114.5</v>
+        <v>85.3</v>
       </c>
       <c r="O147">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P147">
         <v>0</v>
@@ -10025,22 +10025,22 @@
         <v>0</v>
       </c>
       <c r="J148">
-        <v>36.7</v>
+        <v>36.3</v>
       </c>
       <c r="K148">
         <v>40</v>
       </c>
       <c r="L148">
-        <v>76.7</v>
+        <v>76.3</v>
       </c>
       <c r="M148">
         <v>0</v>
       </c>
       <c r="N148">
-        <v>114.2</v>
+        <v>84.3</v>
       </c>
       <c r="O148">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P148">
         <v>0</v>
@@ -10075,37 +10075,37 @@
         <v>0</v>
       </c>
       <c r="E149">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F149">
         <v>0</v>
       </c>
       <c r="G149">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H149">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="I149">
         <v>0</v>
       </c>
       <c r="J149">
-        <v>36.4</v>
+        <v>36</v>
       </c>
       <c r="K149">
         <v>40</v>
       </c>
       <c r="L149">
-        <v>76.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="M149">
         <v>0</v>
       </c>
       <c r="N149">
-        <v>112.4</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="O149">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P149">
         <v>0</v>
@@ -10155,22 +10155,22 @@
         <v>0</v>
       </c>
       <c r="J150">
-        <v>35</v>
+        <v>34.6</v>
       </c>
       <c r="K150">
         <v>40</v>
       </c>
       <c r="L150">
-        <v>75</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M150">
         <v>0</v>
       </c>
       <c r="N150">
-        <v>112.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="O150">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P150">
         <v>0</v>
@@ -10220,40 +10220,40 @@
         <v>0</v>
       </c>
       <c r="J151">
-        <v>34.9</v>
+        <v>34.5</v>
       </c>
       <c r="K151">
         <v>40</v>
       </c>
       <c r="L151">
-        <v>74.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="M151">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N151">
-        <v>132.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="O151">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q151">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S151">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="T151">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="U151">
-        <v>0</v>
+        <v>0.2361809045226131</v>
       </c>
     </row>
     <row r="152" spans="1:21">
@@ -10282,25 +10282,25 @@
         <v>-0.4</v>
       </c>
       <c r="I152">
-        <v>19.9</v>
+        <v>15.2</v>
       </c>
       <c r="J152">
-        <v>34.9</v>
+        <v>34.5</v>
       </c>
       <c r="K152">
         <v>40</v>
       </c>
       <c r="L152">
-        <v>94.8</v>
+        <v>89.8</v>
       </c>
       <c r="M152">
         <v>0</v>
       </c>
       <c r="N152">
-        <v>135.1</v>
+        <v>102</v>
       </c>
       <c r="O152">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P152">
         <v>0</v>
@@ -10347,25 +10347,25 @@
         <v>-0.7</v>
       </c>
       <c r="I153">
-        <v>19.5</v>
+        <v>14.8</v>
       </c>
       <c r="J153">
-        <v>34.9</v>
+        <v>34.5</v>
       </c>
       <c r="K153">
         <v>40</v>
       </c>
       <c r="L153">
-        <v>94.40000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="M153">
         <v>0</v>
       </c>
       <c r="N153">
-        <v>134.3</v>
+        <v>101.4</v>
       </c>
       <c r="O153">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="P153">
         <v>0</v>
@@ -10412,25 +10412,25 @@
         <v>-1.1</v>
       </c>
       <c r="I154">
-        <v>18.8</v>
+        <v>14.1</v>
       </c>
       <c r="J154">
-        <v>34.9</v>
+        <v>34.5</v>
       </c>
       <c r="K154">
         <v>40</v>
       </c>
       <c r="L154">
-        <v>93.7</v>
+        <v>88.7</v>
       </c>
       <c r="M154">
         <v>0</v>
       </c>
       <c r="N154">
-        <v>133.1</v>
+        <v>100.5</v>
       </c>
       <c r="O154">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="P154">
         <v>0</v>
